--- a/Sample_Project/設計書/A1_プロジェクト管理システム/020_方式設計/020_開発標準/020_テスト標準/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
+++ b/Sample_Project/設計書/A1_プロジェクト管理システム/020_方式設計/020_開発標準/020_テスト標準/単体テスト仕様書(画面)_(取引ID)_(取引名).xlsx
@@ -12790,8 +12790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -12832,8 +12832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -12868,8 +12868,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -12906,8 +12906,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -12940,8 +12940,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -12974,8 +12974,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -13008,8 +13008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -13042,8 +13042,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -13080,8 +13080,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -13114,8 +13114,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -13148,8 +13148,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -13184,8 +13184,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -13218,8 +13218,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -13252,8 +13252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -13286,8 +13286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -13324,8 +13324,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -13358,8 +13358,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -13396,8 +13396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -13430,8 +13430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -13466,8 +13466,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -13500,8 +13500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -13534,8 +13534,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -13568,8 +13568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -13604,8 +13604,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -13638,8 +13638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -13674,8 +13674,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -13712,8 +13712,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -13744,8 +13744,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -13776,8 +13776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -13808,8 +13808,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -13844,8 +13844,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -13876,8 +13876,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -13918,8 +13918,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -13952,8 +13952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -13986,8 +13986,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -14022,8 +14022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -14056,8 +14056,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -14090,8 +14090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -14126,8 +14126,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -14160,8 +14160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -14196,8 +14196,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -14230,8 +14230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -14264,8 +14264,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -14298,8 +14298,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -14332,8 +14332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -14366,8 +14366,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -14402,8 +14402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -14438,8 +14438,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -14474,8 +14474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -14512,8 +14512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -14546,8 +14546,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -14580,8 +14580,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -14614,8 +14614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -14648,8 +14648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -14684,8 +14684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -14718,8 +14718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -14752,8 +14752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -14786,8 +14786,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -14820,8 +14820,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -14854,8 +14854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -14888,8 +14888,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -14922,8 +14922,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -14958,8 +14958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -14994,8 +14994,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -15028,8 +15028,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -15062,8 +15062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -15096,8 +15096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -15130,8 +15130,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -15170,8 +15170,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -15204,8 +15204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -15240,8 +15240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -15276,8 +15276,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -15310,8 +15310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -15346,8 +15346,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -15382,8 +15382,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -15422,8 +15422,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -15458,8 +15458,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -15494,8 +15494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -15534,8 +15534,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -15568,8 +15568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -15604,8 +15604,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -15640,8 +15640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -15674,8 +15674,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -15710,8 +15710,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -15750,8 +15750,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -15784,8 +15784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -15818,8 +15818,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -15852,8 +15852,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -15886,8 +15886,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -15922,8 +15922,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -15956,8 +15956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -15990,8 +15990,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -16024,8 +16024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -16058,8 +16058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -16094,8 +16094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -16136,8 +16136,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -16176,8 +16176,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -16210,8 +16210,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -16250,8 +16250,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -16290,8 +16290,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -16324,8 +16324,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -16364,8 +16364,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -16398,8 +16398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -16430,8 +16430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -16462,8 +16462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -16496,8 +16496,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -16528,8 +16528,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -16560,8 +16560,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -16592,8 +16592,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -16626,8 +16626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -16660,8 +16660,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -16692,8 +16692,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -16726,8 +16726,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -16760,8 +16760,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -16794,8 +16794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -16828,8 +16828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -16864,8 +16864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -16904,8 +16904,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -16938,8 +16938,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -16970,8 +16970,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -17002,8 +17002,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -17044,8 +17044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -17080,8 +17080,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -17114,8 +17114,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -17148,8 +17148,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -17184,8 +17184,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -17218,8 +17218,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -17254,8 +17254,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -17292,8 +17292,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -17326,8 +17326,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -17360,8 +17360,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -17396,8 +17396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -17430,8 +17430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -17466,8 +17466,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -17500,8 +17500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -17534,8 +17534,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -17568,8 +17568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -17602,8 +17602,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -17636,8 +17636,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -17672,8 +17672,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -17704,8 +17704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -17738,8 +17738,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -17770,8 +17770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -17802,8 +17802,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -17834,8 +17834,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -17866,8 +17866,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -17898,8 +17898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -17930,8 +17930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -17962,8 +17962,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -17994,8 +17994,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -18026,8 +18026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -18058,8 +18058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -18092,8 +18092,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -18124,8 +18124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -18156,8 +18156,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -18188,8 +18188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -18220,8 +18220,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -18254,8 +18254,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -18288,8 +18288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -18322,8 +18322,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -18354,8 +18354,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -18386,8 +18386,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -18418,8 +18418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -18450,8 +18450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -18482,8 +18482,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -18516,8 +18516,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -18550,8 +18550,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -18584,8 +18584,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -18618,8 +18618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -18654,8 +18654,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -18696,8 +18696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -18734,8 +18734,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -18772,8 +18772,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -18814,8 +18814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -18850,8 +18850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -18884,8 +18884,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -18920,8 +18920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -18954,8 +18954,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -18992,8 +18992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -19032,8 +19032,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -19066,8 +19066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -19100,8 +19100,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -19134,8 +19134,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -19168,8 +19168,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -19202,8 +19202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -19236,8 +19236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -19272,8 +19272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -19310,8 +19310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -19344,8 +19344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -19378,8 +19378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -19412,8 +19412,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -19446,8 +19446,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -19480,8 +19480,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -19514,8 +19514,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -19548,8 +19548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -19582,8 +19582,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -19616,8 +19616,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -19650,8 +19650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -19684,8 +19684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -19718,8 +19718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -19756,8 +19756,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -19790,8 +19790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -19824,8 +19824,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -19858,8 +19858,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -19892,8 +19892,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -19926,8 +19926,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -19960,8 +19960,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -19994,8 +19994,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -20028,8 +20028,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -20062,8 +20062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -20096,8 +20096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -20130,8 +20130,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -20164,8 +20164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -20198,8 +20198,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -20232,8 +20232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -20268,8 +20268,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -20302,8 +20302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -20336,8 +20336,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -20372,8 +20372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -20408,8 +20408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -20450,8 +20450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -20486,8 +20486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -20520,8 +20520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -20554,8 +20554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -20588,8 +20588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -20622,8 +20622,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -20658,8 +20658,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -20692,8 +20692,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -20726,8 +20726,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -20760,8 +20760,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -20794,8 +20794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -20830,8 +20830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -20870,8 +20870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -20912,8 +20912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -20946,8 +20946,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -20984,8 +20984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -21018,8 +21018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -21058,8 +21058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -21094,8 +21094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -21130,8 +21130,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -21166,8 +21166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -21204,8 +21204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -21238,8 +21238,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -21274,8 +21274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -21308,8 +21308,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -21342,8 +21342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -21376,8 +21376,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -21410,8 +21410,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -21444,8 +21444,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -21478,8 +21478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -21512,8 +21512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -21546,8 +21546,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -21580,8 +21580,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -21614,8 +21614,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -21650,8 +21650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -21684,8 +21684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -21718,8 +21718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -21752,8 +21752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -21786,8 +21786,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -21820,8 +21820,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -21856,8 +21856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -21890,8 +21890,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -21924,8 +21924,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -21958,8 +21958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -21992,8 +21992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -22026,8 +22026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -22060,8 +22060,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -22094,8 +22094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -22130,8 +22130,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -22170,8 +22170,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -22202,8 +22202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -22234,8 +22234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -22266,8 +22266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -22304,8 +22304,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -22338,8 +22338,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -22372,8 +22372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -22406,8 +22406,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -22442,8 +22442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -22474,8 +22474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -22506,8 +22506,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -22538,8 +22538,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -22570,8 +22570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -22602,8 +22602,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -22634,8 +22634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -22666,8 +22666,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -22868,8 +22868,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -22910,8 +22910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -22946,8 +22946,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -22984,8 +22984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -23018,8 +23018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -23052,8 +23052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -23086,8 +23086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -23120,8 +23120,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -23158,8 +23158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -23192,8 +23192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -23226,8 +23226,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -23262,8 +23262,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -23296,8 +23296,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -23330,8 +23330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -23364,8 +23364,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -23402,8 +23402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -23436,8 +23436,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -23474,8 +23474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -23508,8 +23508,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -23544,8 +23544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -23578,8 +23578,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -23612,8 +23612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -23646,8 +23646,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -23682,8 +23682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -23716,8 +23716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -23752,8 +23752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -23792,8 +23792,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -23826,8 +23826,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -23860,8 +23860,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -23894,8 +23894,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -23932,8 +23932,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -23966,8 +23966,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -24006,8 +24006,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -24038,8 +24038,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -24070,8 +24070,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -24104,8 +24104,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -24136,8 +24136,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -24168,8 +24168,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -24202,8 +24202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -24234,8 +24234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -24268,8 +24268,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -24300,8 +24300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -24332,8 +24332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -24364,8 +24364,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -24396,8 +24396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -24428,8 +24428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -24462,8 +24462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -24496,8 +24496,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -24530,8 +24530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -24566,8 +24566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -24598,8 +24598,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -24630,8 +24630,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -24662,8 +24662,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -24694,8 +24694,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -24728,8 +24728,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -24760,8 +24760,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -24792,8 +24792,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -24824,8 +24824,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -24856,8 +24856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -24888,8 +24888,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -24920,8 +24920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -24952,8 +24952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -24986,8 +24986,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -25020,8 +25020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -25052,8 +25052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -25084,8 +25084,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -25116,8 +25116,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -25150,8 +25150,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -25188,8 +25188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -25220,8 +25220,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -25254,8 +25254,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -25288,8 +25288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -25320,8 +25320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -25354,8 +25354,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -25388,8 +25388,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -25426,8 +25426,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -25460,8 +25460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -25494,8 +25494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -25532,8 +25532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -25564,8 +25564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -25598,8 +25598,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -25632,8 +25632,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -25664,8 +25664,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -25698,8 +25698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -25736,8 +25736,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -25768,8 +25768,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -25800,8 +25800,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -25832,8 +25832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -25864,8 +25864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -25898,8 +25898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -25930,8 +25930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -25962,8 +25962,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -25994,8 +25994,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -26026,8 +26026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -26060,8 +26060,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -26100,8 +26100,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -26138,8 +26138,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -26170,8 +26170,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -26208,8 +26208,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -26246,8 +26246,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -26278,8 +26278,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -26318,8 +26318,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -26352,8 +26352,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -26384,8 +26384,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -26416,8 +26416,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -26452,8 +26452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -26486,8 +26486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -26520,8 +26520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -26554,8 +26554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -26588,8 +26588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -26624,8 +26624,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -26658,8 +26658,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -26692,8 +26692,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -26726,8 +26726,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -26760,8 +26760,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -26796,8 +26796,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -26832,8 +26832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -26872,8 +26872,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -26908,8 +26908,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -26942,8 +26942,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -26976,8 +26976,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -27016,8 +27016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -27052,8 +27052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -27086,8 +27086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -27120,8 +27120,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -27154,8 +27154,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -27186,8 +27186,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -27222,8 +27222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -27262,8 +27262,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -27298,8 +27298,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -27334,8 +27334,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -27370,8 +27370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -27406,8 +27406,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -27442,8 +27442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -27476,8 +27476,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -27510,8 +27510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -27544,8 +27544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -27578,8 +27578,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -27612,8 +27612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -27650,8 +27650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -27684,8 +27684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -27720,8 +27720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -27754,8 +27754,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -27788,8 +27788,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -27822,8 +27822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -27856,8 +27856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -27890,8 +27890,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -27924,8 +27924,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -27958,8 +27958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -27992,8 +27992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -28026,8 +28026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -28060,8 +28060,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -28096,8 +28096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -28130,8 +28130,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -28164,8 +28164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -28198,8 +28198,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -28232,8 +28232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -28266,8 +28266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -28300,8 +28300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -28336,8 +28336,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -28370,8 +28370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -28404,8 +28404,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -28438,8 +28438,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -28472,8 +28472,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -28504,8 +28504,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -28538,8 +28538,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -28572,8 +28572,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -28606,8 +28606,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -28642,8 +28642,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -28678,8 +28678,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -28720,8 +28720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -28758,8 +28758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -28796,8 +28796,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -28838,8 +28838,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -28874,8 +28874,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -28908,8 +28908,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -28944,8 +28944,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -28978,8 +28978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -29016,8 +29016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -29056,8 +29056,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -29090,8 +29090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -29124,8 +29124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -29158,8 +29158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -29192,8 +29192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -29226,8 +29226,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -29260,8 +29260,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -29296,8 +29296,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -29334,8 +29334,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -29368,8 +29368,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -29402,8 +29402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -29436,8 +29436,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -29470,8 +29470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -29504,8 +29504,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -29538,8 +29538,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -29572,8 +29572,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -29606,8 +29606,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -29640,8 +29640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -29674,8 +29674,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -29708,8 +29708,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -29742,8 +29742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -29780,8 +29780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -29814,8 +29814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -29848,8 +29848,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -29882,8 +29882,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -29916,8 +29916,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -29950,8 +29950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -29984,8 +29984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -30018,8 +30018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -30052,8 +30052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -30086,8 +30086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -30120,8 +30120,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -30154,8 +30154,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -30188,8 +30188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -30222,8 +30222,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -30256,8 +30256,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -30292,8 +30292,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -30326,8 +30326,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -30360,8 +30360,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -30396,8 +30396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -30432,8 +30432,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -30474,8 +30474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -30510,8 +30510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -30544,8 +30544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -30578,8 +30578,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -30612,8 +30612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -30646,8 +30646,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -30682,8 +30682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -30716,8 +30716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -30750,8 +30750,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -30784,8 +30784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -30818,8 +30818,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -30854,8 +30854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -30894,8 +30894,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -30936,8 +30936,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -30970,8 +30970,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -31008,8 +31008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -31042,8 +31042,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -31082,8 +31082,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -31118,8 +31118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -31154,8 +31154,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -31190,8 +31190,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -31228,8 +31228,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -31262,8 +31262,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -31298,8 +31298,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -31332,8 +31332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -31366,8 +31366,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -31400,8 +31400,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -31434,8 +31434,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -31468,8 +31468,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -31502,8 +31502,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -31536,8 +31536,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -31570,8 +31570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -31604,8 +31604,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -31638,8 +31638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -31674,8 +31674,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -31708,8 +31708,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -31742,8 +31742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -31776,8 +31776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -31810,8 +31810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -31844,8 +31844,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -31880,8 +31880,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -31914,8 +31914,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -31948,8 +31948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -31982,8 +31982,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -32016,8 +32016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -32050,8 +32050,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -32084,8 +32084,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -32118,8 +32118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -32154,8 +32154,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -32194,8 +32194,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -32226,8 +32226,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -32258,8 +32258,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -32290,8 +32290,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -32328,8 +32328,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -32362,8 +32362,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -32396,8 +32396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -32430,8 +32430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -32466,8 +32466,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -32498,8 +32498,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -32530,8 +32530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -32562,8 +32562,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -32594,8 +32594,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -32626,8 +32626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -32658,8 +32658,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -32690,8 +32690,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -32722,8 +32722,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -32764,8 +32764,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-2-1</v>
       </c>
@@ -32798,8 +32798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-3-1</v>
       </c>
@@ -32830,8 +32830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-4-1</v>
       </c>
@@ -32862,8 +32862,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-5-1</v>
       </c>
@@ -32894,8 +32894,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-6-1</v>
       </c>
@@ -32926,8 +32926,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-7-1</v>
       </c>
@@ -32958,8 +32958,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-8-1</v>
       </c>
@@ -32990,8 +32990,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-9-1</v>
       </c>
@@ -33022,8 +33022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-10-1</v>
       </c>
@@ -33054,8 +33054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-11-1</v>
       </c>
@@ -33086,8 +33086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-12-1</v>
       </c>
@@ -33118,8 +33118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-13-1</v>
       </c>
@@ -33150,8 +33150,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-14-1</v>
       </c>
@@ -33182,8 +33182,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-15-1</v>
       </c>
@@ -33214,8 +33214,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-16-1</v>
       </c>
@@ -33246,8 +33246,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-17-1</v>
       </c>
@@ -33278,8 +33278,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-18-1</v>
       </c>
@@ -33310,8 +33310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-19-1</v>
       </c>
@@ -33342,8 +33342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-20-1</v>
       </c>
@@ -33374,8 +33374,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-21-1</v>
       </c>
@@ -33408,8 +33408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -33442,8 +33442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-2-1</v>
       </c>
@@ -33474,8 +33474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -33508,8 +33508,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F320),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F320)&gt;0)*ROW($F$11:F320),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J320),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-2-1</v>
       </c>
@@ -33540,8 +33540,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F321),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F321)&gt;0)*ROW($F$11:F321),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J321),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -33574,8 +33574,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F322),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F322)&gt;0)*ROW($F$11:F322),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J322),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -33608,8 +33608,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F323),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F323)&gt;0)*ROW($F$11:F323),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J323),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -33640,8 +33640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F324),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F324)&gt;0)*ROW($F$11:F324),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J324),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -33672,8 +33672,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F325),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F325)&gt;0)*ROW($F$11:F325),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J325),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-4-1</v>
       </c>
@@ -33704,8 +33704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F326),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F326)&gt;0)*ROW($F$11:F326),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J326),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-5-1</v>
       </c>
@@ -33736,8 +33736,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F327),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F327)&gt;0)*ROW($F$11:F327),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J327),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-6-1</v>
       </c>
@@ -33768,8 +33768,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F328),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F328)&gt;0)*ROW($F$11:F328),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J328),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-7-1</v>
       </c>
@@ -33800,8 +33800,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F329),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F329)&gt;0)*ROW($F$11:F329),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J329),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-8-1</v>
       </c>
@@ -33832,8 +33832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F330),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F330)&gt;0)*ROW($F$11:F330),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J330),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-9-1</v>
       </c>
@@ -33864,8 +33864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F331),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F331)&gt;0)*ROW($F$11:F331),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J331),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -33898,8 +33898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F332),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F332)&gt;0)*ROW($F$11:F332),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J332),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -33932,8 +33932,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F333),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F333)&gt;0)*ROW($F$11:F333),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J333),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -33968,8 +33968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F334),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F334)&gt;0)*ROW($F$11:F334),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J334),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-1-1</v>
       </c>
@@ -34002,8 +34002,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F335),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F335)&gt;0)*ROW($F$11:F335),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J335),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-2-1</v>
       </c>
@@ -34034,8 +34034,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F336),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F336)&gt;0)*ROW($F$11:F336),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J336),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-3-1</v>
       </c>
@@ -34066,8 +34066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F337),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F337)&gt;0)*ROW($F$11:F337),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J337),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-4-1</v>
       </c>
@@ -34098,8 +34098,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F338),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F338)&gt;0)*ROW($F$11:F338),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J338),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-1-1</v>
       </c>
@@ -34134,8 +34134,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F339),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F339)&gt;0)*ROW($F$11:F339),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J339),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-2-1</v>
       </c>
@@ -34166,8 +34166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F340),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F340)&gt;0)*ROW($F$11:F340),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J340),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-3-1</v>
       </c>
@@ -34198,8 +34198,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F341),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F341)&gt;0)*ROW($F$11:F341),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J341),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-1-1</v>
       </c>
@@ -34234,8 +34234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F342),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F342)&gt;0)*ROW($F$11:F342),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J342),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-2-1</v>
       </c>
@@ -34266,8 +34266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F343),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F343)&gt;0)*ROW($F$11:F343),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J343),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-3-1</v>
       </c>
@@ -34298,8 +34298,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F344),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F344)&gt;0)*ROW($F$11:F344),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J344),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-4-1</v>
       </c>
@@ -34330,8 +34330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F345),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F345)&gt;0)*ROW($F$11:F345),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J345),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-5-1</v>
       </c>
@@ -34362,8 +34362,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F346),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F346)&gt;0)*ROW($F$11:F346),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J346),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-6-1</v>
       </c>
@@ -34396,8 +34396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F347),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F347)&gt;0)*ROW($F$11:F347),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J347),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-7-1</v>
       </c>
@@ -34428,8 +34428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F348),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F348)&gt;0)*ROW($F$11:F348),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J348),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-8-1</v>
       </c>
@@ -34460,8 +34460,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F349),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F349)&gt;0)*ROW($F$11:F349),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J349),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-9-1</v>
       </c>
@@ -34492,8 +34492,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F350),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F350)&gt;0)*ROW($F$11:F350),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J350),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-10-1</v>
       </c>
@@ -34524,8 +34524,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F351),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F351)&gt;0)*ROW($F$11:F351),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J351),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-11-1</v>
       </c>
@@ -34556,8 +34556,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F352),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F352)&gt;0)*ROW($F$11:F352),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J352),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-12-1</v>
       </c>
@@ -34588,8 +34588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F353),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F353)&gt;0)*ROW($F$11:F353),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J353),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-13-1</v>
       </c>
@@ -34620,8 +34620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F354),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F354)&gt;0)*ROW($F$11:F354),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J354),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>111-14-1</v>
       </c>
@@ -34652,8 +34652,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F355),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F355)&gt;0)*ROW($F$11:F355),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J355),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-1-1</v>
       </c>
@@ -34686,8 +34686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F356),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F356)&gt;0)*ROW($F$11:F356),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J356),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-2-1</v>
       </c>
@@ -34718,8 +34718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F357),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F357)&gt;0)*ROW($F$11:F357),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J357),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-3-1</v>
       </c>
@@ -34750,8 +34750,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F358),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F358)&gt;0)*ROW($F$11:F358),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J358),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-4-1</v>
       </c>
@@ -34782,8 +34782,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F359),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F359)&gt;0)*ROW($F$11:F359),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J359),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-5-1</v>
       </c>
@@ -34814,8 +34814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F360),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F360)&gt;0)*ROW($F$11:F360),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J360),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-6-1</v>
       </c>
@@ -34846,8 +34846,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F361),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F361)&gt;0)*ROW($F$11:F361),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J361),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>112-7-1</v>
       </c>
@@ -34878,8 +34878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F362),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F362)&gt;0)*ROW($F$11:F362),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J362),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-1-1</v>
       </c>
@@ -34918,8 +34918,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F363),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F363)&gt;0)*ROW($F$11:F363),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J363),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-2-1</v>
       </c>
@@ -34950,8 +34950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F364),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F364)&gt;0)*ROW($F$11:F364),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J364),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-3-1</v>
       </c>
@@ -34982,8 +34982,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F365),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F365)&gt;0)*ROW($F$11:F365),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J365),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-4-1</v>
       </c>
@@ -35014,8 +35014,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F366),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F366)&gt;0)*ROW($F$11:F366),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J366),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>113-5-1</v>
       </c>
@@ -35048,8 +35048,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F367),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F367)&gt;0)*ROW($F$11:F367),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J367),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-1-1</v>
       </c>
@@ -35084,8 +35084,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F368),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F368)&gt;0)*ROW($F$11:F368),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J368),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-2-1</v>
       </c>
@@ -35116,8 +35116,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F369),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F369)&gt;0)*ROW($F$11:F369),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J369),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-3-1</v>
       </c>
@@ -35150,8 +35150,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F370),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F370)&gt;0)*ROW($F$11:F370),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J370),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-4-1</v>
       </c>
@@ -35182,8 +35182,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F371),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F371)&gt;0)*ROW($F$11:F371),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J371),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>114-5-1</v>
       </c>
@@ -35214,8 +35214,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F372),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F372)&gt;0)*ROW($F$11:F372),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J372),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-1-1</v>
       </c>
@@ -35252,8 +35252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F373),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F373)&gt;0)*ROW($F$11:F373),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J373),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-2-1</v>
       </c>
@@ -35284,8 +35284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F374),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F374)&gt;0)*ROW($F$11:F374),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J374),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-3-1</v>
       </c>
@@ -35316,8 +35316,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F375),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F375)&gt;0)*ROW($F$11:F375),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J375),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-4-1</v>
       </c>
@@ -35348,8 +35348,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F376),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F376)&gt;0)*ROW($F$11:F376),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J376),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-5-1</v>
       </c>
@@ -35382,8 +35382,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F377),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F377)&gt;0)*ROW($F$11:F377),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J377),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>115-6-1</v>
       </c>
@@ -35414,8 +35414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F378),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F378)&gt;0)*ROW($F$11:F378),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J378),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>116-1-1</v>
       </c>
@@ -35450,8 +35450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F379),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F379)&gt;0)*ROW($F$11:F379),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J379),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>117-1-1</v>
       </c>
@@ -35486,8 +35486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F380),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F380)&gt;0)*ROW($F$11:F380),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J380),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>118-1-1</v>
       </c>
@@ -35522,8 +35522,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F381),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F381)&gt;0)*ROW($F$11:F381),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J381),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>119-1-1</v>
       </c>
@@ -35562,8 +35562,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F382),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F382)&gt;0)*ROW($F$11:F382),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J382),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>119-2-1</v>
       </c>
@@ -35755,11 +35755,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D11),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E11),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E11)&gt;0)*ROW($E$11:E11),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -35791,11 +35791,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D12),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E12),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E12)&gt;0)*ROW($E$11:E12),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -35823,11 +35823,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D13),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E13),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E13)&gt;0)*ROW($E$11:E13),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -35857,11 +35857,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D14),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E14),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E14)&gt;0)*ROW($E$11:E14),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -35889,11 +35889,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D15),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E15),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E15)&gt;0)*ROW($E$11:E15),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -35923,11 +35923,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D16),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D16)&gt;0)*ROW($D$11:D16),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E16),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E16)&gt;0)*ROW($E$11:E16),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -35957,11 +35957,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D17),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D17)&gt;0)*ROW($D$11:D17),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E17),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E17)&gt;0)*ROW($E$11:E17),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -35991,11 +35991,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D18),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D18)&gt;0)*ROW($D$11:D18),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E18),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E18)&gt;0)*ROW($E$11:E18),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -36025,11 +36025,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D19),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D19)&gt;0)*ROW($D$11:D19),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E19),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E19)&gt;0)*ROW($E$11:E19),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -36061,11 +36061,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D20),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D20)&gt;0)*ROW($D$11:D20),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E20),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E20)&gt;0)*ROW($E$11:E20),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -36095,11 +36095,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D21),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D21)&gt;0)*ROW($D$11:D21),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E21),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E21)&gt;0)*ROW($E$11:E21),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -36128,11 +36128,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D22),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D22)&gt;0)*ROW($D$11:D22),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E22),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E22)&gt;0)*ROW($E$11:E22),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -36163,11 +36163,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D23),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D23)&gt;0)*ROW($D$11:D23),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E23),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E23)&gt;0)*ROW($E$11:E23),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -36196,11 +36196,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D24),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D24)&gt;0)*ROW($D$11:D24),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E24),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E24)&gt;0)*ROW($E$11:E24),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -36231,11 +36231,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D25),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D25)&gt;0)*ROW($D$11:D25),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E25),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E25)&gt;0)*ROW($E$11:E25),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -36262,11 +36262,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D26),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D26)&gt;0)*ROW($D$11:D26),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E26),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E26)&gt;0)*ROW($E$11:E26),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -36295,11 +36295,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D27),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D27)&gt;0)*ROW($D$11:D27),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E27),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E27)&gt;0)*ROW($E$11:E27),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -36326,11 +36326,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D28),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D28)&gt;0)*ROW($D$11:D28),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E28),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E28)&gt;0)*ROW($E$11:E28),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -36363,11 +36363,11 @@
 _xlpm.確認観点2数, COUNTA($D$11:D29),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D29)&gt;0)*ROW($D$11:D29),0)),
 _xlpm.確認観点3数, COUNTA(INDIRECT("E"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):E29),
-_xlpm.確認観点3数（確認観点3が空の場合は1）,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
+_xlpm.確認観点3数_空なら1,IF(_xlpm.確認観点3数=0,1,_xlpm.確認観点3数),
 _xlpm.直近で確認観点3が空でないセルの行番号, MAX(INDEX((LEN($E$11:E29)&gt;0)*ROW($E$11:E29),0),_xlpm.直近で確認観点2が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("I"&amp;_xlpm.直近で確認観点3が空でないセルの行番号):I29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数（確認観点3が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点2が空でないセルの行番号&gt;_xlpm.直近で確認観点3が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点2数&amp;"-"&amp;_xlpm.確認観点3数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
